--- a/product_selector_out/STM32L151-152.xlsx
+++ b/product_selector_out/STM32L151-152.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -85,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -99,6 +104,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3597,7 +3603,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4911,7 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5892,7 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6219,7 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7854,7 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11118,7 +11124,7 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15696,7 +15702,7 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -16350,7 +16356,7 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19620,7 +19626,7 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20928,7 +20934,7 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22236,7 +22242,7 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23451,9 +23457,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="7" t="inlineStr">
@@ -23778,9 +23784,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="7" t="inlineStr">
@@ -24105,9 +24111,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="7" t="inlineStr">
@@ -24432,9 +24438,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="7" t="inlineStr">
@@ -24759,9 +24765,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX16" s="7" t="inlineStr">
@@ -25086,9 +25092,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="7" t="inlineStr">
@@ -25413,9 +25419,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX18" s="7" t="inlineStr">
@@ -25520,9 +25526,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -25740,14 +25746,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -25820,9 +25826,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -26067,9 +26073,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX20" s="7" t="inlineStr">
@@ -26394,9 +26400,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX21" s="7" t="inlineStr">
@@ -26721,9 +26727,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX22" s="7" t="inlineStr">
@@ -26828,9 +26834,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -27048,14 +27054,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -27128,9 +27134,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -27375,9 +27381,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX24" s="7" t="inlineStr">
@@ -27702,9 +27708,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX25" s="7" t="inlineStr">
@@ -27809,9 +27815,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -28029,14 +28035,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY26" s="6" t="inlineStr">
@@ -28109,9 +28115,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -28136,9 +28142,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -28356,14 +28362,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY27" s="6" t="inlineStr">
@@ -28436,9 +28442,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -28683,9 +28689,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX28" s="7" t="inlineStr">
@@ -29010,9 +29016,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX29" s="7" t="inlineStr">
@@ -29337,9 +29343,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX30" s="7" t="inlineStr">
@@ -29664,9 +29670,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX31" s="7" t="inlineStr">
@@ -29771,9 +29777,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -29991,14 +29997,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY32" s="6" t="inlineStr">
@@ -30071,9 +30077,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -30318,9 +30324,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX33" s="7" t="inlineStr">
@@ -30645,9 +30651,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX34" s="7" t="inlineStr">
@@ -30972,9 +30978,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX35" s="7" t="inlineStr">
@@ -31299,9 +31305,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX36" s="7" t="inlineStr">
@@ -31626,9 +31632,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX37" s="7" t="inlineStr">
@@ -31953,9 +31959,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX38" s="7" t="inlineStr">
@@ -32280,9 +32286,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX39" s="7" t="inlineStr">
@@ -32607,9 +32613,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX40" s="7" t="inlineStr">
@@ -32934,9 +32940,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX41" s="7" t="inlineStr">
@@ -33041,9 +33047,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -33261,14 +33267,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY42" s="6" t="inlineStr">
@@ -33341,9 +33347,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -33588,9 +33594,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX43" s="7" t="inlineStr">
@@ -33915,9 +33921,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX44" s="7" t="inlineStr">
@@ -34242,9 +34248,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX45" s="7" t="inlineStr">
@@ -34569,9 +34575,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX46" s="7" t="inlineStr">
@@ -34896,9 +34902,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX47" s="7" t="inlineStr">
@@ -35223,9 +35229,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX48" s="7" t="inlineStr">
@@ -35550,9 +35556,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW49" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX49" s="7" t="inlineStr">
@@ -35877,9 +35883,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW50" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW50" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX50" s="7" t="inlineStr">
@@ -36204,9 +36210,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW51" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW51" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX51" s="7" t="inlineStr">
@@ -36531,9 +36537,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW52" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW52" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX52" s="7" t="inlineStr">
@@ -36858,9 +36864,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW53" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW53" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX53" s="7" t="inlineStr">
@@ -37185,9 +37191,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX54" s="7" t="inlineStr">
@@ -37512,9 +37518,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW55" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW55" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX55" s="7" t="inlineStr">
@@ -37619,9 +37625,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -37839,14 +37845,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY56" s="6" t="inlineStr">
@@ -37919,9 +37925,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -38166,9 +38172,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW57" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX57" s="7" t="inlineStr">
@@ -38273,9 +38279,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -38493,14 +38499,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY58" s="6" t="inlineStr">
@@ -38573,9 +38579,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -38820,9 +38826,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW59" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX59" s="7" t="inlineStr">
@@ -39147,9 +39153,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX60" s="7" t="inlineStr">
@@ -39474,9 +39480,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX61" s="7" t="inlineStr">
@@ -39801,9 +39807,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX62" s="7" t="inlineStr">
@@ -40128,9 +40134,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW63" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW63" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX63" s="7" t="inlineStr">
@@ -40455,9 +40461,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX64" s="7" t="inlineStr">
@@ -40782,9 +40788,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX65" s="7" t="inlineStr">
@@ -41109,9 +41115,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW66" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW66" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX66" s="7" t="inlineStr">
@@ -41436,9 +41442,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX67" s="7" t="inlineStr">
@@ -41543,9 +41549,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -41763,14 +41769,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY68" s="6" t="inlineStr">
@@ -41843,9 +41849,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -42090,9 +42096,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW69" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX69" s="7" t="inlineStr">
@@ -42417,9 +42423,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX70" s="7" t="inlineStr">
@@ -42744,9 +42750,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW71" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX71" s="7" t="inlineStr">
@@ -42851,9 +42857,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -43071,14 +43077,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY72" s="6" t="inlineStr">
@@ -43151,9 +43157,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -43398,9 +43404,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW73" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX73" s="7" t="inlineStr">
@@ -43725,9 +43731,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX74" s="7" t="inlineStr">
@@ -44052,9 +44058,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW75" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW75" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX75" s="7" t="inlineStr">
@@ -44159,9 +44165,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -44379,14 +44385,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY76" s="6" t="inlineStr">
@@ -44459,9 +44465,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44706,9 +44712,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW77" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW77" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX77" s="7" t="inlineStr">
@@ -44807,7 +44813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -44838,7 +44844,1216 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STM32L151CB</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32L151VD-X</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32L152CB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32L151C8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32L152C8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32L152QE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32L152RE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32L151VE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32L151ZE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32L151C6-A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32L152UC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32L151R8-A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32L151QE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32L151R6-A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32L151RE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32L152ZE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32L151C8-A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32L152VC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32L152QC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32L151QC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32L152ZC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32L151ZC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32L151CC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32L151RB-A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32L151R6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32L152CC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32L151RC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32L151VC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32L152RC</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32L152QD</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32L151QD</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32L152R8</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32L151ZD</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32L152ZD</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32L152RD</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32L151RD</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32L152C6</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32L152VD</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32L151VD</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32L152R6</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STM32L151C6</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32L151VB</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32L152VB</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32L151V8</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32L152V8</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32L151RB</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32L152RB</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32L151V8-A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32L151VB-A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32L151RC-A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32L151CB-A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>STM32L151UC</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32L151R8</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32L152VE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32L151VC-A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32L151-152.xlsx
+++ b/product_selector_out/STM32L151-152.xlsx
@@ -3603,7 +3603,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -16356,7 +16356,7 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -22242,7 +22242,7 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
         </is>
       </c>
     </row>
@@ -25526,9 +25526,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -25746,14 +25746,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -25826,9 +25826,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -26834,9 +26834,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -27054,14 +27054,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -27134,9 +27134,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -27815,9 +27815,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -28035,14 +28035,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY26" s="6" t="inlineStr">
@@ -28115,9 +28115,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -28142,9 +28142,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -28362,14 +28362,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY27" s="6" t="inlineStr">
@@ -28442,9 +28442,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -29777,9 +29777,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -29997,14 +29997,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY32" s="6" t="inlineStr">
@@ -30077,9 +30077,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -33047,9 +33047,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -33267,14 +33267,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY42" s="6" t="inlineStr">
@@ -33347,9 +33347,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -37625,9 +37625,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -37845,14 +37845,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW56" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX56" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY56" s="6" t="inlineStr">
@@ -37925,9 +37925,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -38279,9 +38279,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -38499,14 +38499,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX58" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY58" s="6" t="inlineStr">
@@ -38579,9 +38579,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -41549,9 +41549,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -41769,14 +41769,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY68" s="6" t="inlineStr">
@@ -41849,9 +41849,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -42857,9 +42857,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -43077,14 +43077,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY72" s="6" t="inlineStr">
@@ -43157,9 +43157,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -44165,9 +44165,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -44385,14 +44385,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW76" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY76" s="6" t="inlineStr">
@@ -44465,9 +44465,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -44813,7 +44813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -45001,7 +45001,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32L151VE</t>
+          <t>STM32L152C6-A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -45016,14 +45016,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32L151ZE</t>
+          <t>STM32L151VE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -45045,7 +45045,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32L151C6-A</t>
+          <t>STM32L151ZE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -45067,7 +45067,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32L152UC</t>
+          <t>STM32L151C6-A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -45082,14 +45082,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32L151R8-A</t>
+          <t>STM32L152VC-A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -45111,7 +45111,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32L151QE</t>
+          <t>STM32L152UC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -45126,14 +45126,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L151R6-A</t>
+          <t>STM32L151R8-A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -45155,7 +45155,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L151RE</t>
+          <t>STM32L152VD-X</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -45170,14 +45170,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L152ZE</t>
+          <t>STM32L152R6-A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -45192,14 +45192,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L151C8-A</t>
+          <t>STM32L151QE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -45221,7 +45221,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L152VC</t>
+          <t>STM32L151R6-A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -45236,14 +45236,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L152QC</t>
+          <t>STM32L151RE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -45265,7 +45265,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L151QC</t>
+          <t>STM32L152ZE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -45287,7 +45287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L152ZC</t>
+          <t>STM32L152C8-A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -45302,14 +45302,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L151ZC</t>
+          <t>STM32L151C8-A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -45331,7 +45331,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L151CC</t>
+          <t>STM32L152VC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -45353,7 +45353,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L151RB-A</t>
+          <t>STM32L152QC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -45375,7 +45375,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L151R6</t>
+          <t>STM32L151QC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -45397,7 +45397,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L152CC</t>
+          <t>STM32L152ZC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -45412,14 +45412,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L151RC</t>
+          <t>STM32L151ZC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -45434,14 +45434,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L151VC</t>
+          <t>STM32L151CC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -45463,7 +45463,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L152RC</t>
+          <t>STM32L151RB-A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -45478,14 +45478,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L152QD</t>
+          <t>STM32L151R6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -45507,7 +45507,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L151QD</t>
+          <t>STM32L152R8-A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -45522,14 +45522,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L152R8</t>
+          <t>STM32L152CC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -45544,14 +45544,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L151ZD</t>
+          <t>STM32L151RC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -45566,14 +45566,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L152ZD</t>
+          <t>STM32L151VC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -45588,14 +45588,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L152RD</t>
+          <t>STM32L152RC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -45610,14 +45610,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L151RD</t>
+          <t>STM32L152QD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -45639,7 +45639,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L152C6</t>
+          <t>STM32L151QD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -45661,7 +45661,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L152VD</t>
+          <t>STM32L152R8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -45683,7 +45683,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L151VD</t>
+          <t>STM32L151ZD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -45705,7 +45705,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L152R6</t>
+          <t>STM32L152ZD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -45727,7 +45727,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L151C6</t>
+          <t>STM32L152RD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -45749,7 +45749,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L151VB</t>
+          <t>STM32L151RD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -45771,7 +45771,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L152VB</t>
+          <t>STM32L152C6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -45793,7 +45793,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L151V8</t>
+          <t>STM32L152VD</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -45815,7 +45815,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L152V8</t>
+          <t>STM32L152CB-A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -45830,14 +45830,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L151RB</t>
+          <t>STM32L151VD</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -45859,7 +45859,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L152RB</t>
+          <t>STM32L152V8-A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -45874,14 +45874,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L151V8-A</t>
+          <t>STM32L152R6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -45903,7 +45903,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L151VB-A</t>
+          <t>STM32L151C6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -45925,7 +45925,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L151RC-A</t>
+          <t>STM32L151VB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -45947,7 +45947,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L151CB-A</t>
+          <t>STM32L152VB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -45969,7 +45969,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L151UC</t>
+          <t>STM32L151V8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -45984,14 +45984,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L151R8</t>
+          <t>STM32L152V8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -46013,7 +46013,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L152VE</t>
+          <t>STM32L151RB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -46035,20 +46035,262 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>STM32L152RB</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32L151V8-A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32L152VB-A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32L151VB-A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32L151RC-A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STM32L151CB-A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>STM32L152RB-A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>STM32L151UC</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>STM32L151R8</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>STM32L152VE</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>STM32L152RC-A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>STM32L151VC-A</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>

--- a/product_selector_out/STM32L151-152.xlsx
+++ b/product_selector_out/STM32L151-152.xlsx
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -16356,7 +16356,7 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19953,7 +19953,7 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
     </row>
@@ -20280,7 +20280,7 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22242,7 +22242,7 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22569,7 +22569,7 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
     </row>
@@ -25526,9 +25526,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -25746,14 +25746,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -25826,9 +25826,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -26834,9 +26834,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -27054,14 +27054,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -27134,9 +27134,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -27488,9 +27488,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -27708,14 +27708,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY25" s="6" t="inlineStr">
@@ -27788,9 +27788,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -27815,9 +27815,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -28035,14 +28035,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY26" s="6" t="inlineStr">
@@ -28115,9 +28115,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -28142,9 +28142,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -28362,14 +28362,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY27" s="6" t="inlineStr">
@@ -28442,9 +28442,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -28796,9 +28796,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -29016,14 +29016,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY29" s="6" t="inlineStr">
@@ -29096,9 +29096,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -29777,9 +29777,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -29997,14 +29997,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY32" s="6" t="inlineStr">
@@ -30077,9 +30077,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -32393,9 +32393,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -32613,14 +32613,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY40" s="6" t="inlineStr">
@@ -32693,9 +32693,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -33047,9 +33047,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -33267,14 +33267,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY42" s="6" t="inlineStr">
@@ -33347,9 +33347,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -37625,9 +37625,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -37845,14 +37845,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW56" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY56" s="6" t="inlineStr">
@@ -37925,9 +37925,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -38279,9 +38279,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -38499,14 +38499,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW58" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY58" s="6" t="inlineStr">
@@ -38579,9 +38579,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41549,9 +41549,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -41769,14 +41769,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY68" s="6" t="inlineStr">
@@ -41849,9 +41849,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -42203,9 +42203,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -42423,14 +42423,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY70" s="6" t="inlineStr">
@@ -42503,9 +42503,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -42857,9 +42857,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -43077,14 +43077,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY72" s="6" t="inlineStr">
@@ -43157,9 +43157,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44165,9 +44165,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -44385,14 +44385,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW76" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY76" s="6" t="inlineStr">
@@ -44465,9 +44465,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44813,7 +44813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -44884,7 +44884,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -45001,7 +45001,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32L152C6-A</t>
+          <t>STM32L151VE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -45016,14 +45016,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32L151VE</t>
+          <t>STM32L151ZE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -45045,7 +45045,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32L151ZE</t>
+          <t>STM32L151C6-A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -45067,7 +45067,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32L151C6-A</t>
+          <t>STM32L152UC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -45082,14 +45082,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32L152VC-A</t>
+          <t>STM32L151QE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -45111,7 +45111,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32L152UC</t>
+          <t>STM32L151RE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -45126,14 +45126,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L151R8-A</t>
+          <t>STM32L152ZE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -45155,7 +45155,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L152VD-X</t>
+          <t>STM32L151C8-A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -45170,14 +45170,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L152R6-A</t>
+          <t>STM32L152VC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -45199,7 +45199,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L151QE</t>
+          <t>STM32L152QC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -45221,7 +45221,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L151R6-A</t>
+          <t>STM32L151QC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -45243,7 +45243,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L151RE</t>
+          <t>STM32L152ZC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -45265,7 +45265,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L152ZE</t>
+          <t>STM32L151ZC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -45287,7 +45287,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L152C8-A</t>
+          <t>STM32L151CC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -45309,7 +45309,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L151C8-A</t>
+          <t>STM32L151R6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -45331,7 +45331,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L152VC</t>
+          <t>STM32L152CC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -45353,7 +45353,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L152QC</t>
+          <t>STM32L151RC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -45368,14 +45368,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L151QC</t>
+          <t>STM32L151VC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -45390,14 +45390,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L152ZC</t>
+          <t>STM32L152RC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -45412,14 +45412,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L151ZC</t>
+          <t>STM32L152QD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -45441,7 +45441,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L151CC</t>
+          <t>STM32L151QD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -45456,14 +45456,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L151RB-A</t>
+          <t>STM32L152R8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -45485,7 +45485,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L151R6</t>
+          <t>STM32L151ZD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -45507,7 +45507,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L152R8-A</t>
+          <t>STM32L152ZD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -45522,14 +45522,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L152CC</t>
+          <t>STM32L152RD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -45544,14 +45544,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L151RC</t>
+          <t>STM32L151RD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -45566,14 +45566,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L151VC</t>
+          <t>STM32L152C6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -45588,14 +45588,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L152RC</t>
+          <t>STM32L152VD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -45610,14 +45610,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L152QD</t>
+          <t>STM32L151VD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -45639,7 +45639,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L151QD</t>
+          <t>STM32L152R6</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -45661,7 +45661,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L152R8</t>
+          <t>STM32L151C6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -45683,7 +45683,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L151ZD</t>
+          <t>STM32L151VB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -45705,7 +45705,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L152ZD</t>
+          <t>STM32L152VB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -45727,7 +45727,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L152RD</t>
+          <t>STM32L151V8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -45749,7 +45749,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L151RD</t>
+          <t>STM32L152V8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -45771,7 +45771,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L152C6</t>
+          <t>STM32L151RB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -45793,7 +45793,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L152VD</t>
+          <t>STM32L152RB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -45815,7 +45815,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L152CB-A</t>
+          <t>STM32L151V8-A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -45830,14 +45830,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L151VD</t>
+          <t>STM32L151VB-A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -45852,14 +45852,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L152V8-A</t>
+          <t>STM32L151CB-A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -45874,14 +45874,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L152R6</t>
+          <t>STM32L151UC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -45896,14 +45896,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L151C6</t>
+          <t>STM32L151R8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -45925,7 +45925,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L151VB</t>
+          <t>STM32L152VE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -45947,7 +45947,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L152VB</t>
+          <t>STM32L151VC-A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -45962,337 +45962,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32L151V8</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32L152V8</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32L151RB</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32L152RB</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32L151V8-A</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32L152VB-A</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32L151VB-A</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32L151RC-A</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>STM32L151CB-A</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>STM32L152RB-A</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>STM32L151UC</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>STM32L151R8</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>STM32L152VE</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>STM32L152RC-A</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>STM32L151VC-A</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32L151-152.xlsx
+++ b/product_selector_out/STM32L151-152.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM77"/>
+  <dimension ref="A1:BN77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.1171875" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -3606,6 +3648,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -4914,6 +4976,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -5568,6 +5640,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5895,6 +5972,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -6222,6 +6304,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -6876,6 +6968,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -7857,6 +7964,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
         </is>
       </c>
@@ -9489,6 +9621,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
         </is>
       </c>
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
         </is>
       </c>
@@ -10143,6 +10285,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -10473,6 +10620,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -10797,6 +10949,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -11127,6 +11284,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -11451,6 +11613,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -11778,6 +11945,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -12105,6 +12277,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -12432,6 +12609,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -12759,6 +12941,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -13086,6 +13273,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -13413,6 +13605,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -13740,6 +13937,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -14067,6 +14269,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -14394,6 +14601,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -14721,6 +14933,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -15048,6 +15265,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -15375,6 +15597,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -15705,6 +15932,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -16029,6 +16261,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -16359,6 +16596,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -16683,6 +16925,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -17010,6 +17257,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -17337,6 +17589,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -17664,6 +17921,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -17991,6 +18253,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -18318,6 +18585,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -18645,6 +18917,11 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -18972,6 +19249,11 @@
       </c>
       <c r="BM66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -19299,6 +19581,11 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
@@ -19629,6 +19916,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN68" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -19953,6 +20245,11 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
@@ -20283,6 +20580,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN70" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -20607,6 +20909,11 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -20937,6 +21244,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN72" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -21261,6 +21573,11 @@
       </c>
       <c r="BM73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -21588,6 +21905,11 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -21915,6 +22237,11 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -22245,6 +22572,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN76" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -22569,12 +22901,17 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -22595,16 +22932,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -22617,6 +22952,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -22636,7 +22972,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -22719,7 +23057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM77"/>
+  <dimension ref="A1:BN77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22787,6 +23125,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23120,6 +23459,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -23215,6 +23559,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -23537,7 +23882,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23864,7 +24214,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24191,7 +24546,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24518,7 +24878,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24845,7 +25210,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25172,7 +25542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25499,7 +25874,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25831,6 +26211,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -26153,7 +26538,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26480,7 +26870,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26807,7 +27202,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27139,6 +27539,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -27461,7 +27866,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27793,6 +28203,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -28120,6 +28535,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -28447,6 +28867,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -28769,7 +29194,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29101,6 +29531,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -29423,7 +29858,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29750,7 +30190,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30082,6 +30527,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -30404,7 +30854,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30731,7 +31186,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31058,7 +31518,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31385,7 +31850,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31712,7 +32182,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32039,7 +32514,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32366,7 +32846,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32698,6 +33183,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -33020,7 +33510,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33352,6 +33847,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -33674,7 +34174,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34001,7 +34506,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34328,7 +34838,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34655,7 +35170,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34982,7 +35502,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35309,7 +35834,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35636,7 +36166,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35963,7 +36498,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36290,7 +36830,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36617,7 +37162,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36944,7 +37494,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37271,7 +37826,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37598,7 +38158,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37930,6 +38495,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -38252,7 +38822,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38584,6 +39159,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -38906,7 +39486,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39233,7 +39818,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39560,7 +40150,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39887,7 +40482,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40214,7 +40814,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40541,7 +41146,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40868,7 +41478,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41195,7 +41810,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM66" s="6" t="inlineStr">
+      <c r="BM66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41522,7 +42142,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
+      <c r="BM67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41854,6 +42479,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -42176,7 +42806,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
+      <c r="BM69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42508,6 +43143,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -42830,7 +43470,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
+      <c r="BM71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43162,6 +43807,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -43484,7 +44134,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM73" s="6" t="inlineStr">
+      <c r="BM73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43811,7 +44466,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
+      <c r="BM74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44138,7 +44798,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
+      <c r="BM75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44470,6 +45135,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -44792,7 +45462,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM77" s="6" t="inlineStr">
+      <c r="BM77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44800,8 +45475,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
